--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="SPV" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPV!$A$1:$C$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPV!$A$1:$C$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="125">
   <si>
     <t>SPV</t>
   </si>
@@ -1752,7 +1752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="17.4285714285714" customWidth="1"/>
@@ -2241,7 +2241,7 @@
         <v>47</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" ht="15.75" spans="1:3">
@@ -2252,7 +2252,7 @@
         <v>47</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
@@ -2262,19 +2262,19 @@
       <c r="B46" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>52</v>
+      <c r="C46" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="47" ht="15.75" spans="1:3">
-      <c r="A47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>53</v>
+      <c r="A47" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="48" ht="15.75" spans="1:3">
@@ -2285,7 +2285,7 @@
         <v>55</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" ht="15.75" spans="1:3">
@@ -2296,7 +2296,7 @@
         <v>55</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" ht="15.75" spans="1:3">
@@ -2307,7 +2307,7 @@
         <v>55</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" ht="15.75" spans="1:3">
@@ -2318,7 +2318,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" ht="15.75" spans="1:3">
@@ -2326,10 +2326,10 @@
         <v>54</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" ht="15.75" spans="1:3">
@@ -2340,7 +2340,7 @@
         <v>61</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="1:3">
@@ -2351,7 +2351,7 @@
         <v>61</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" ht="15.75" spans="1:3">
@@ -2362,7 +2362,7 @@
         <v>61</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:3">
@@ -2373,7 +2373,7 @@
         <v>61</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:3">
@@ -2384,18 +2384,18 @@
         <v>61</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" ht="15.75" spans="1:3">
       <c r="A58" s="17" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:3">
@@ -2406,7 +2406,7 @@
         <v>69</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:3">
@@ -2417,7 +2417,7 @@
         <v>69</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:3">
@@ -2428,7 +2428,7 @@
         <v>69</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:3">
@@ -2439,18 +2439,18 @@
         <v>69</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" ht="15.75" spans="1:3">
       <c r="A63" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="19" t="s">
-        <v>74</v>
+      <c r="C63" s="21" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:3">
@@ -2461,7 +2461,7 @@
         <v>69</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:3">
@@ -2472,7 +2472,7 @@
         <v>69</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
@@ -2483,7 +2483,7 @@
         <v>69</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:3">
@@ -2494,7 +2494,7 @@
         <v>69</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:3">
@@ -2505,7 +2505,7 @@
         <v>69</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:3">
@@ -2516,18 +2516,18 @@
         <v>69</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:3">
       <c r="A70" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="21" t="s">
-        <v>81</v>
+      <c r="C70" s="23" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:3">
@@ -2538,7 +2538,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
@@ -2549,7 +2549,7 @@
         <v>69</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:3">
@@ -2560,7 +2560,7 @@
         <v>69</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:3">
@@ -2568,10 +2568,10 @@
         <v>68</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:3">
@@ -2582,7 +2582,7 @@
         <v>86</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:3">
@@ -2593,7 +2593,7 @@
         <v>86</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" ht="15.75" spans="1:3">
@@ -2604,7 +2604,7 @@
         <v>86</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" ht="15.75" spans="1:3">
@@ -2615,7 +2615,7 @@
         <v>86</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:3">
@@ -2626,7 +2626,7 @@
         <v>86</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" ht="15.75" spans="1:3">
@@ -2637,7 +2637,7 @@
         <v>86</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:3">
@@ -2645,10 +2645,10 @@
         <v>68</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:3">
@@ -2659,7 +2659,7 @@
         <v>94</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" ht="15.75" spans="1:3">
@@ -2670,7 +2670,7 @@
         <v>94</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:3">
@@ -2681,7 +2681,7 @@
         <v>94</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" ht="15.75" spans="1:3">
@@ -2692,7 +2692,7 @@
         <v>94</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" ht="15.75" spans="1:3">
@@ -2703,7 +2703,7 @@
         <v>94</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:3">
@@ -2714,7 +2714,7 @@
         <v>94</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" ht="15.75" spans="1:3">
@@ -2725,7 +2725,7 @@
         <v>94</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" ht="15.75" spans="1:3">
@@ -2736,7 +2736,7 @@
         <v>94</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:3">
@@ -2747,7 +2747,7 @@
         <v>94</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91" ht="15.75" spans="1:3">
@@ -2758,7 +2758,7 @@
         <v>94</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" ht="15.75" spans="1:3">
@@ -2769,7 +2769,7 @@
         <v>94</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" ht="15.75" spans="1:3">
@@ -2780,18 +2780,18 @@
         <v>94</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" ht="15.75" spans="1:3">
       <c r="A94" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B94" s="22" t="s">
+      <c r="B94" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="23" t="s">
-        <v>107</v>
+      <c r="C94" s="15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:3">
@@ -2802,7 +2802,7 @@
         <v>94</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" ht="15.75" spans="1:3">
@@ -2813,7 +2813,7 @@
         <v>94</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
@@ -2824,7 +2824,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" ht="15.75" spans="1:3">
@@ -2835,7 +2835,7 @@
         <v>94</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:3">
@@ -2846,18 +2846,18 @@
         <v>94</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" spans="1:3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C100" s="15" t="s">
-        <v>113</v>
+      <c r="C100" s="24" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2867,8 +2867,8 @@
       <c r="B101" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C101" s="24" t="s">
-        <v>114</v>
+      <c r="C101" s="25" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2878,19 +2878,19 @@
       <c r="B102" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C102" s="25" t="s">
-        <v>115</v>
+      <c r="C102" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C103" s="26" t="s">
-        <v>116</v>
+      <c r="C103" s="25" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2900,8 +2900,8 @@
       <c r="B104" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C104" s="25" t="s">
-        <v>117</v>
+      <c r="C104" s="24" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2909,10 +2909,10 @@
         <v>68</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C105" s="24" t="s">
-        <v>118</v>
+        <v>47</v>
+      </c>
+      <c r="C105" s="25" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2922,8 +2922,8 @@
       <c r="B106" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C106" s="25" t="s">
-        <v>119</v>
+      <c r="C106" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2933,8 +2933,8 @@
       <c r="B107" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C107" s="24" t="s">
-        <v>120</v>
+      <c r="C107" s="25" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2944,8 +2944,8 @@
       <c r="B108" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C108" s="25" t="s">
-        <v>121</v>
+      <c r="C108" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2955,8 +2955,8 @@
       <c r="B109" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C109" s="24" t="s">
-        <v>122</v>
+      <c r="C109" s="25" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2966,22 +2966,14 @@
       <c r="B110" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C110" s="25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C111" s="24" t="s">
+      <c r="C110" s="24" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C110" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="C2:C8">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
@@ -2998,15 +2990,15 @@
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C48:C63">
+  <conditionalFormatting sqref="C47:C62">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C64:C70">
+  <conditionalFormatting sqref="C63:C69">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C71:C94">
+  <conditionalFormatting sqref="C70:C93">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -7,11 +7,8 @@
     <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
-    <sheet name="SPV" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SPV!$A$1:$C$110</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="130">
   <si>
     <t>SPV</t>
   </si>
@@ -68,6 +65,12 @@
     <t>CMX-Victoria.pdv</t>
   </si>
   <si>
+    <t>CMX-Naranjo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Bolivar.pdv</t>
+  </si>
+  <si>
     <t>CDMEX002</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>CMX-VillaHermosa.pdv</t>
   </si>
   <si>
+    <t>CMX-Cadiz.pdv</t>
+  </si>
+  <si>
     <t>CDMEX003</t>
   </si>
   <si>
@@ -290,6 +296,9 @@
     <t>CMX-TorreBlanca.pdv</t>
   </si>
   <si>
+    <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
     <t>CDMEX005</t>
   </si>
   <si>
@@ -312,6 +321,9 @@
   </si>
   <si>
     <t>CMX-SantaCruz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaRosa.pdv</t>
   </si>
   <si>
     <t>CDMEX006</t>
@@ -417,17 +429,10 @@
     <numFmt numFmtId="176" formatCode="_-\$* #,##0.00_-;\-\$* #,##0.00_-;_-\$* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-\$* #,##0_-;\-\$* #,##0_-;_-\$* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -447,16 +452,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <sz val="12"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -603,7 +609,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,61 +678,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor theme="4" tint="0.799981688894314"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,6 +756,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -768,18 +780,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -822,12 +858,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -872,19 +914,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1005,217 +1034,211 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1752,1258 +1775,1363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C110"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:C115"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="17.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="26.4285714285714" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
+    <col min="2" max="2" width="12.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="27.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="15.75" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="15.75" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="15.75" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="15.75" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="15.75" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" ht="15.75" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="8" ht="15.75" spans="1:3">
+      <c r="A8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+    </row>
+    <row r="10" ht="15.75" spans="1:3">
+      <c r="A10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="15.75" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    <row r="11" ht="15.75" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" ht="15.75" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:3">
-      <c r="A12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:3">
-      <c r="A13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="A13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:3">
-      <c r="A14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="9" t="s">
+    </row>
+    <row r="15" ht="15.75" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="9" t="s">
+    <row r="16" ht="15.75" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="1:3">
-      <c r="A16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="9" t="s">
+    <row r="17" ht="15.75" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" ht="15.75" spans="1:3">
-      <c r="A17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="15.75" spans="1:3">
-      <c r="A18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="A18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" ht="15.75" spans="1:3">
-      <c r="A19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="A19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" ht="15.75" spans="1:3">
-      <c r="A20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="A20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" ht="15.75" spans="1:3">
-      <c r="A21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="12" t="s">
+    </row>
+    <row r="22" ht="15.75" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="12" t="s">
+    <row r="23" ht="15.75" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="15.75" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="12" t="s">
+    <row r="24" ht="15.75" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" ht="15.75" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="12" t="s">
+      <c r="A25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" ht="15.75" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="12" t="s">
+      <c r="A26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" ht="15.75" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="12" t="s">
+      <c r="A27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="A28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="29" ht="15.75" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="12" t="s">
+      <c r="A29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" ht="15.75" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="A30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="12" t="s">
+      <c r="A31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" ht="15.75" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="A32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" ht="15.75" spans="1:3">
-      <c r="A33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="12" t="s">
+      <c r="A33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="12" t="s">
+      <c r="A34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" ht="15.75" spans="1:3">
-      <c r="A35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="13" t="s">
+      <c r="A35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" ht="15.75" spans="1:3">
-      <c r="A36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="37" ht="15.75" spans="1:3">
-      <c r="A37" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:3">
-      <c r="A38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>26</v>
+      <c r="A38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="39" ht="15.75" spans="1:3">
-      <c r="A39" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="1:3">
-      <c r="A40" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="41" ht="15.75" spans="1:3">
-      <c r="A41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="15" t="s">
+    </row>
+    <row r="42" ht="15.75" spans="1:3">
+      <c r="A42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" ht="15.75" spans="1:3">
-      <c r="A42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="15" t="s">
+    <row r="43" ht="15.75" spans="1:3">
+      <c r="A43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="43" ht="15.75" spans="1:3">
-      <c r="A43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="15" t="s">
+    <row r="44" ht="15.75" spans="1:3">
+      <c r="A44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" spans="1:3">
-      <c r="A44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="45" ht="15.75" spans="1:3">
-      <c r="A45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="15" t="s">
+      <c r="A45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="46" ht="15.75" spans="1:3">
-      <c r="A46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="A46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="47" ht="15.75" spans="1:3">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="18" t="s">
+    </row>
+    <row r="48" ht="15.75" spans="1:3">
+      <c r="A48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="19" t="s">
+    </row>
+    <row r="49" ht="15.75" spans="1:3">
+      <c r="A49" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" ht="15.75" spans="1:3">
-      <c r="A48" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="19" t="s">
+    <row r="50" ht="15.75" spans="1:3">
+      <c r="A50" s="16" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="49" ht="15.75" spans="1:3">
-      <c r="A49" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="19" t="s">
+      <c r="B50" s="17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="50" ht="15.75" spans="1:3">
-      <c r="A50" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="18" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="51" ht="15.75" spans="1:3">
-      <c r="A51" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="52" ht="15.75" spans="1:3">
-      <c r="A52" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="18" t="s">
+      <c r="A52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="19" t="s">
+    </row>
+    <row r="53" ht="15.75" spans="1:3">
+      <c r="A53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" ht="15.75" spans="1:3">
-      <c r="A53" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="19" t="s">
+    <row r="54" ht="15.75" spans="1:3">
+      <c r="A54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="54" ht="15.75" spans="1:3">
-      <c r="A54" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="19" t="s">
+    <row r="55" ht="15.75" spans="1:3">
+      <c r="A55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="55" ht="15.75" spans="1:3">
-      <c r="A55" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:3">
-      <c r="A56" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="19" t="s">
+      <c r="A56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="57" ht="15.75" spans="1:3">
-      <c r="A57" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="19" t="s">
+      <c r="A57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="58" ht="15.75" spans="1:3">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="18" t="s">
+    </row>
+    <row r="59" ht="15.75" spans="1:3">
+      <c r="A59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C58" s="19" t="s">
+    </row>
+    <row r="60" ht="15.75" spans="1:3">
+      <c r="A60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="18" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:3">
-      <c r="A59" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" spans="1:3">
-      <c r="A60" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="19" t="s">
+    <row r="61" ht="15.75" spans="1:3">
+      <c r="A61" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="19" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" spans="1:3">
-      <c r="A61" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="62" ht="15.75" spans="1:3">
-      <c r="A62" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="C62" s="19" t="s">
+      <c r="A62" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="63" ht="15.75" spans="1:3">
-      <c r="A63" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" s="21" t="s">
+      <c r="A63" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:3">
-      <c r="A64" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C64" s="21" t="s">
+      <c r="A64" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="65" ht="15.75" spans="1:3">
-      <c r="A65" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C65" s="21" t="s">
+      <c r="A65" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="66" ht="15.75" spans="1:3">
-      <c r="A66" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="21" t="s">
+      <c r="A66" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:3">
-      <c r="A67" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" s="21" t="s">
+      <c r="A67" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:3">
-      <c r="A68" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="21" t="s">
+      <c r="A68" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:3">
-      <c r="A69" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="21" t="s">
+      <c r="A69" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="20" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:3">
-      <c r="A70" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="23" t="s">
+      <c r="A70" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" s="20" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="71" ht="15.75" spans="1:3">
-      <c r="A71" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C71" s="23" t="s">
+      <c r="A71" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="20" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="72" ht="15.75" spans="1:3">
-      <c r="A72" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C72" s="23" t="s">
+      <c r="A72" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="20" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:3">
-      <c r="A73" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C73" s="23" t="s">
+      <c r="A73" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" s="20" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:3">
-      <c r="A74" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74" s="22" t="s">
+      <c r="A74" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C74" s="23" t="s">
+    </row>
+    <row r="75" ht="15.75" spans="1:3">
+      <c r="A75" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C75" s="20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:3">
-      <c r="A75" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B75" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" s="23" t="s">
+    <row r="76" ht="15.75" spans="1:3">
+      <c r="A76" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:3">
-      <c r="A76" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B76" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" s="23" t="s">
+    <row r="77" ht="15.75" spans="1:3">
+      <c r="A77" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="77" ht="15.75" spans="1:3">
-      <c r="A77" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B77" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C77" s="23" t="s">
+    <row r="78" ht="15.75" spans="1:3">
+      <c r="A78" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" s="21" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="78" ht="15.75" spans="1:3">
-      <c r="A78" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="22" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:3">
-      <c r="A79" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C79" s="23" t="s">
+      <c r="A79" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79" s="22" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="80" ht="15.75" spans="1:3">
-      <c r="A80" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" s="23" t="s">
+      <c r="A80" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:3">
-      <c r="A81" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B81" s="22" t="s">
+      <c r="A81" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="C81" s="23" t="s">
+    </row>
+    <row r="82" ht="15.75" spans="1:3">
+      <c r="A82" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="22" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="82" ht="15.75" spans="1:3">
-      <c r="A82" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B82" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C82" s="23" t="s">
+    <row r="83" ht="15.75" spans="1:3">
+      <c r="A83" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="22" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="83" ht="15.75" spans="1:3">
-      <c r="A83" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B83" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" s="23" t="s">
+    <row r="84" ht="15.75" spans="1:3">
+      <c r="A84" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C84" s="22" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" ht="15.75" spans="1:3">
-      <c r="A84" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B84" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C84" s="23" t="s">
+    <row r="85" ht="15.75" spans="1:3">
+      <c r="A85" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" s="22" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="85" ht="15.75" spans="1:3">
-      <c r="A85" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B85" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C85" s="23" t="s">
+    <row r="86" ht="15.75" spans="1:3">
+      <c r="A86" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" spans="1:3">
-      <c r="A86" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B86" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="14" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:3">
-      <c r="A87" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B87" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C87" s="23" t="s">
+      <c r="A87" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C87" s="14" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="88" ht="15.75" spans="1:3">
-      <c r="A88" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B88" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C88" s="23" t="s">
+      <c r="A88" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="89" ht="15.75" spans="1:3">
-      <c r="A89" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B89" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C89" s="23" t="s">
+      <c r="A89" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="14" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:3">
-      <c r="A90" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B90" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C90" s="23" t="s">
+      <c r="A90" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90" s="14" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="91" ht="15.75" spans="1:3">
-      <c r="A91" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B91" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C91" s="23" t="s">
+      <c r="A91" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="14" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="92" ht="15.75" spans="1:3">
-      <c r="A92" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B92" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C92" s="23" t="s">
+      <c r="A92" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C92" s="14" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="93" ht="15.75" spans="1:3">
-      <c r="A93" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B93" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" s="23" t="s">
+      <c r="A93" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" s="14" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="94" ht="15.75" spans="1:3">
-      <c r="A94" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C94" s="15" t="s">
+      <c r="A94" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" s="14" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:3">
-      <c r="A95" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C95" s="15" t="s">
+      <c r="A95" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C95" s="14" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="96" ht="15.75" spans="1:3">
-      <c r="A96" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" s="15" t="s">
+      <c r="A96" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" s="14" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="97" ht="15.75" spans="1:3">
-      <c r="A97" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" s="15" t="s">
+      <c r="A97" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" s="14" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="98" ht="15.75" spans="1:3">
-      <c r="A98" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C98" s="15" t="s">
+      <c r="A98" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:3">
-      <c r="A99" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C99" s="15" t="s">
+      <c r="A99" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99" s="14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C100" s="24" t="s">
+    <row r="100" ht="15.75" spans="1:3">
+      <c r="A100" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" s="14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C101" s="25" t="s">
+    <row r="101" ht="15.75" spans="1:3">
+      <c r="A101" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" s="14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C102" s="26" t="s">
+    <row r="102" ht="15.75" spans="1:3">
+      <c r="A102" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C102" s="14" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C103" s="25" t="s">
+    <row r="103" ht="15.75" spans="1:3">
+      <c r="A103" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C103" s="14" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C104" s="24" t="s">
+    <row r="104" ht="15.75" spans="1:3">
+      <c r="A104" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C104" s="14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C105" s="25" t="s">
+    <row r="105" ht="15.75" spans="1:3">
+      <c r="A105" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105" s="14" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C106" s="24" t="s">
+    <row r="106" ht="15.75" spans="1:3">
+      <c r="A106" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" s="14" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C107" s="25" t="s">
+    <row r="107" ht="15.75" spans="1:3">
+      <c r="A107" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107" s="14" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C108" s="24" t="s">
+    <row r="108" ht="15.75" spans="1:3">
+      <c r="A108" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C108" s="14" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C109" s="25" t="s">
+    <row r="109" ht="15.75" spans="1:3">
+      <c r="A109" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C109" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>47</v>
+    <row r="110" ht="15.75" spans="1:3">
+      <c r="A110" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B110" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="C110" s="24" t="s">
         <v>124</v>
       </c>
     </row>
+    <row r="111" ht="15.75" spans="1:3">
+      <c r="A111" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B111" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" spans="1:3">
+      <c r="A112" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" spans="1:3">
+      <c r="A113" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B113" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" spans="1:3">
+      <c r="A114" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" spans="1:3">
+      <c r="A115" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C110" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <conditionalFormatting sqref="C2:C8">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C61">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C62">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C64">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C67">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C68">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:C13">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  <conditionalFormatting sqref="C70">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C71">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:C20">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="C72">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C73">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C40">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="C74">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C62">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="C76">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C63:C69">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="C2:C8">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:C93">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="C11:C15">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:C43">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C50:C60">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C73:C76 C78:C84">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -609,7 +609,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -756,12 +756,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -780,42 +774,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -853,12 +823,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1106,61 +1070,61 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="132">
   <si>
     <t>SPV</t>
   </si>
@@ -297,6 +297,12 @@
   </si>
   <si>
     <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hocaba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chopo.pdv</t>
   </si>
   <si>
     <t>CDMEX005</t>
@@ -1739,7 +1745,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
@@ -2598,22 +2604,22 @@
       <c r="A78" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B78" s="21" t="s">
+      <c r="B78" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" s="20" t="s">
         <v>90</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:3">
       <c r="A79" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B79" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>92</v>
+      <c r="B79" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="80" ht="15.75" spans="1:3">
@@ -2621,7 +2627,7 @@
         <v>71</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C80" s="22" t="s">
         <v>93</v>
@@ -2632,7 +2638,7 @@
         <v>71</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C81" s="22" t="s">
         <v>94</v>
@@ -2643,7 +2649,7 @@
         <v>71</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>95</v>
@@ -2654,7 +2660,7 @@
         <v>71</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C83" s="22" t="s">
         <v>96</v>
@@ -2665,7 +2671,7 @@
         <v>71</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>97</v>
@@ -2676,7 +2682,7 @@
         <v>71</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C85" s="22" t="s">
         <v>98</v>
@@ -2686,22 +2692,22 @@
       <c r="A86" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" s="22" t="s">
         <v>99</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="87" ht="15.75" spans="1:3">
       <c r="A87" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B87" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>101</v>
+      <c r="B87" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="88" ht="15.75" spans="1:3">
@@ -2709,7 +2715,7 @@
         <v>71</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C88" s="14" t="s">
         <v>102</v>
@@ -2720,7 +2726,7 @@
         <v>71</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C89" s="14" t="s">
         <v>103</v>
@@ -2731,7 +2737,7 @@
         <v>71</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C90" s="14" t="s">
         <v>104</v>
@@ -2742,7 +2748,7 @@
         <v>71</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>105</v>
@@ -2753,7 +2759,7 @@
         <v>71</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C92" s="14" t="s">
         <v>106</v>
@@ -2764,7 +2770,7 @@
         <v>71</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>107</v>
@@ -2775,7 +2781,7 @@
         <v>71</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>108</v>
@@ -2786,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>109</v>
@@ -2797,7 +2803,7 @@
         <v>71</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C96" s="14" t="s">
         <v>110</v>
@@ -2808,7 +2814,7 @@
         <v>71</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>111</v>
@@ -2819,7 +2825,7 @@
         <v>71</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C98" s="14" t="s">
         <v>112</v>
@@ -2830,7 +2836,7 @@
         <v>71</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>113</v>
@@ -2841,7 +2847,7 @@
         <v>71</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C100" s="14" t="s">
         <v>114</v>
@@ -2852,7 +2858,7 @@
         <v>71</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>115</v>
@@ -2863,7 +2869,7 @@
         <v>71</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C102" s="14" t="s">
         <v>116</v>
@@ -2874,7 +2880,7 @@
         <v>71</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>117</v>
@@ -2885,7 +2891,7 @@
         <v>71</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C104" s="14" t="s">
         <v>118</v>
@@ -2896,7 +2902,7 @@
         <v>71</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>119</v>
@@ -2907,7 +2913,7 @@
         <v>71</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C106" s="14" t="s">
         <v>120</v>
@@ -2918,7 +2924,7 @@
         <v>71</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>121</v>
@@ -2929,7 +2935,7 @@
         <v>71</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C108" s="14" t="s">
         <v>122</v>
@@ -2940,7 +2946,7 @@
         <v>71</v>
       </c>
       <c r="B109" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>123</v>
@@ -2950,10 +2956,10 @@
       <c r="A110" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B110" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C110" s="24" t="s">
+      <c r="B110" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2961,10 +2967,10 @@
       <c r="A111" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B111" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C111" s="24" t="s">
+      <c r="B111" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="14" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3012,88 +3018,118 @@
         <v>129</v>
       </c>
     </row>
+    <row r="116" ht="15.75" spans="1:3">
+      <c r="A116" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" spans="1:3">
+      <c r="A117" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C9">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C61">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C62">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C63">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C64">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C66">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C67">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C68">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C69">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C70">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C71">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C72">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C73">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C74">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C75">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C76">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
+  <conditionalFormatting sqref="C78">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
+  <conditionalFormatting sqref="C79">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C61">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C62">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C63">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C64">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C65">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C66">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C67">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C68">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C69">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C70">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C71">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C72">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C73">
+  <conditionalFormatting sqref="C87">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C74">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="C2:C8">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C75">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="C11:C15">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C76">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  <conditionalFormatting sqref="C17:C23">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C77">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="C24:C43">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C85">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C8">
+  <conditionalFormatting sqref="C50:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C15">
+  <conditionalFormatting sqref="C73:C76 C80:C86">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17:C23">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:C43">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C50:C60">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C73:C76 C78:C84">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -1,14 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7620"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$152</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="164">
   <si>
     <t>SPV</t>
   </si>
@@ -206,6 +209,36 @@
     <t>CMX-Loma.pdv</t>
   </si>
   <si>
+    <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cedros.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hocaba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chopo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aragon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Colipo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atitlan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aztecas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Galeana.pdV</t>
+  </si>
+  <si>
+    <t>CMX-Aldama.pdv</t>
+  </si>
+  <si>
     <t>CDMEX005</t>
   </si>
   <si>
@@ -230,6 +263,12 @@
     <t>CMX-Portales.pdv</t>
   </si>
   <si>
+    <t>CMX-LaRosa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LasArmas.pd</t>
+  </si>
+  <si>
     <t>CDMEX006</t>
   </si>
   <si>
@@ -305,6 +344,51 @@
     <t>CMX-Lieja.pdv</t>
   </si>
   <si>
+    <t>CMX-Pirules.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapiceria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Silao.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Circunvalacion.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atlixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
     <t>CDMEX007</t>
   </si>
   <si>
@@ -368,6 +452,36 @@
     <t>CMX-MilpaAlta.pdv</t>
   </si>
   <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdy</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdy</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdy</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
     <t>CDMEX008</t>
   </si>
   <si>
@@ -387,6 +501,9 @@
   </si>
   <si>
     <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
   </si>
   <si>
     <t>ARR-Arriaga.pdv</t>
@@ -412,10 +529,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-\$* #,##0.00_-;\-\$* #,##0.00_-;_-\$* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-\$* #,##0_-;\-\$* #,##0_-;_-\$* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -903,19 +1020,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1593,12 +1710,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C114"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:C152"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
-    <col min="2" max="2" width="12.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="8.42592592592593" customWidth="1"/>
+    <col min="2" max="2" width="12.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="27.5740740740741" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2167,10 +2284,10 @@
         <v>41</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2178,10 +2295,10 @@
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2189,10 +2306,10 @@
         <v>41</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2200,10 +2317,10 @@
         <v>41</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2211,10 +2328,10 @@
         <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2222,10 +2339,10 @@
         <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2233,10 +2350,10 @@
         <v>41</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2244,10 +2361,10 @@
         <v>41</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2255,10 +2372,10 @@
         <v>41</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2266,10 +2383,10 @@
         <v>41</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2277,10 +2394,10 @@
         <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2288,10 +2405,10 @@
         <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -2299,10 +2416,10 @@
         <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2310,10 +2427,10 @@
         <v>41</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2321,10 +2438,10 @@
         <v>41</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2332,10 +2449,10 @@
         <v>41</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -2343,10 +2460,10 @@
         <v>41</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2354,10 +2471,10 @@
         <v>41</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2365,10 +2482,10 @@
         <v>41</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -2376,7 +2493,7 @@
         <v>41</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>80</v>
@@ -2387,7 +2504,7 @@
         <v>41</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>81</v>
@@ -2398,7 +2515,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>82</v>
@@ -2409,7 +2526,7 @@
         <v>41</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>83</v>
@@ -2420,7 +2537,7 @@
         <v>41</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>84</v>
@@ -2431,7 +2548,7 @@
         <v>41</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>85</v>
@@ -2442,7 +2559,7 @@
         <v>41</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>86</v>
@@ -2453,7 +2570,7 @@
         <v>41</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>87</v>
@@ -2464,7 +2581,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>88</v>
@@ -2475,7 +2592,7 @@
         <v>41</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>89</v>
@@ -2486,7 +2603,7 @@
         <v>41</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>90</v>
@@ -2497,7 +2614,7 @@
         <v>41</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>91</v>
@@ -2505,222 +2622,222 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2728,10 +2845,10 @@
         <v>41</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2739,10 +2856,10 @@
         <v>41</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2750,10 +2867,10 @@
         <v>41</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2761,10 +2878,10 @@
         <v>41</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2772,10 +2889,10 @@
         <v>41</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2783,21 +2900,21 @@
         <v>41</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -2805,10 +2922,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -2816,10 +2933,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -2827,10 +2944,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -2838,10 +2955,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -2849,10 +2966,428 @@
         <v>3</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C114" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" t="s">
+        <v>119</v>
+      </c>
+      <c r="C116" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" t="s">
+        <v>119</v>
+      </c>
+      <c r="C117" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" t="s">
+        <v>119</v>
+      </c>
+      <c r="C118" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" t="s">
+        <v>119</v>
+      </c>
+      <c r="C119" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" t="s">
+        <v>119</v>
+      </c>
+      <c r="C120" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" t="s">
+        <v>119</v>
+      </c>
+      <c r="C121" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" t="s">
+        <v>119</v>
+      </c>
+      <c r="C122" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" t="s">
+        <v>119</v>
+      </c>
+      <c r="C123" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" t="s">
+        <v>119</v>
+      </c>
+      <c r="C125" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" t="s">
+        <v>119</v>
+      </c>
+      <c r="C126" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" t="s">
+        <v>119</v>
+      </c>
+      <c r="C127" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" t="s">
+        <v>119</v>
+      </c>
+      <c r="C128" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>3</v>
+      </c>
+      <c r="B129" t="s">
+        <v>119</v>
+      </c>
+      <c r="C129" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>3</v>
+      </c>
+      <c r="B130" t="s">
+        <v>119</v>
+      </c>
+      <c r="C130" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>3</v>
+      </c>
+      <c r="B131" t="s">
+        <v>119</v>
+      </c>
+      <c r="C131" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>3</v>
+      </c>
+      <c r="B132" t="s">
+        <v>119</v>
+      </c>
+      <c r="C132" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>3</v>
+      </c>
+      <c r="B133" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>3</v>
+      </c>
+      <c r="B134" t="s">
+        <v>119</v>
+      </c>
+      <c r="C134" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>3</v>
+      </c>
+      <c r="B135" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>3</v>
+      </c>
+      <c r="B136" t="s">
+        <v>119</v>
+      </c>
+      <c r="C136" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>3</v>
+      </c>
+      <c r="B137" t="s">
+        <v>119</v>
+      </c>
+      <c r="C137" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" t="s">
+        <v>3</v>
+      </c>
+      <c r="B138" t="s">
+        <v>119</v>
+      </c>
+      <c r="C138" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" t="s">
+        <v>3</v>
+      </c>
+      <c r="B139" t="s">
+        <v>119</v>
+      </c>
+      <c r="C139" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" t="s">
+        <v>41</v>
+      </c>
+      <c r="B140" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" t="s">
+        <v>41</v>
+      </c>
+      <c r="B141" t="s">
+        <v>150</v>
+      </c>
+      <c r="C141" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" t="s">
+        <v>41</v>
+      </c>
+      <c r="B142" t="s">
+        <v>150</v>
+      </c>
+      <c r="C142" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" t="s">
+        <v>41</v>
+      </c>
+      <c r="B143" t="s">
+        <v>150</v>
+      </c>
+      <c r="C143" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" t="s">
+        <v>150</v>
+      </c>
+      <c r="C145" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" t="s">
+        <v>150</v>
+      </c>
+      <c r="C146" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" t="s">
+        <v>3</v>
+      </c>
+      <c r="B147" t="s">
+        <v>150</v>
+      </c>
+      <c r="C147" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" t="s">
+        <v>3</v>
+      </c>
+      <c r="B148" t="s">
+        <v>150</v>
+      </c>
+      <c r="C148" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B149" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" t="s">
+        <v>3</v>
+      </c>
+      <c r="B150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" t="s">
+        <v>3</v>
+      </c>
+      <c r="B151" t="s">
+        <v>150</v>
+      </c>
+      <c r="C151" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" t="s">
+        <v>3</v>
+      </c>
+      <c r="B152" t="s">
+        <v>150</v>
+      </c>
+      <c r="C152" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="170">
   <si>
     <t>SPV</t>
   </si>
@@ -47,481 +47,499 @@
     <t>CDMEX001</t>
   </si>
   <si>
+    <t>CMX-Comonfort.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hipodromo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LindaVista.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MargaritaMaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pantaco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanMarcos.pdv</t>
+  </si>
+  <si>
     <t>CMX-Tezozomoc.pdv</t>
   </si>
   <si>
-    <t>CMX-Comonfort.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanMarcos.pdv</t>
-  </si>
-  <si>
     <t>CMX-Victoria.pdv</t>
   </si>
   <si>
-    <t>CMX-Pantaco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MargaritaMaz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LindaVista.pdv</t>
+    <t>CMX-Benavides.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Naranjo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Romana.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Coral.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pino.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaVilla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rosario.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Valenzuela.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX002</t>
+  </si>
+  <si>
+    <t>CMX-Bondojito.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJuan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepeyac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Triunfo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-VillaHermosa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cadiz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Remedios.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Rayon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaViga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Palmira.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX003</t>
+  </si>
+  <si>
+    <t>CMX-Guerrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Obrera.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Roma.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Trebol.pdv</t>
+  </si>
+  <si>
+    <t>CMX-NuevoVallejo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Linares.pdv</t>
   </si>
   <si>
     <t>CMX-Bolivar.pdv</t>
   </si>
   <si>
-    <t>CMX-Naranjo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Romana.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Valenzuela.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Rosario.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Linares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Rayon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaViga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Remedios.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Palmira.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Coral.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pino.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Lavilla.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX002</t>
-  </si>
-  <si>
-    <t>CMX-Triunfo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-VillaHermosa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepeyac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Bondojito.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJuan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cadiz.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX003</t>
-  </si>
-  <si>
-    <t>CMX-Hipodromo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Guerrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Trebol.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Roma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-NuevoVallejo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Obrera.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Benavides.pdv</t>
-  </si>
-  <si>
     <t>DIANA</t>
   </si>
   <si>
     <t>CDMEX004</t>
   </si>
   <si>
+    <t>CMX-Barranca.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cuajimalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Encinos.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Guajiras.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Jalalpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LasAguilas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Loma.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixcoac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Olivar.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaPaz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aragon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Hocaba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Cedros.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aztecas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Galeana.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atacama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Aldama.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Amores.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX005</t>
+  </si>
+  <si>
+    <t>CMX-Alamos.pdv</t>
+  </si>
+  <si>
+    <t>CMX-DelValle.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Division.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Napoles.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pestalozzi.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Portales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaCruz.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Ixcateopan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaRosa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LasArmas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SalinaCruz.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX006</t>
+  </si>
+  <si>
+    <t>CMX-AgricolaOriental.pdv</t>
+  </si>
+  <si>
+    <t>CMX-LaTraviata.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Leyes.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Magdalena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Palmitas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Polvorilla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-RomeroRubio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLorenzo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaIsabel.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Santiago.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepalcates.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Torres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vergel.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vulcanizacion.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zapata.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Lieja.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepito.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Ayala.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Atlixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Circunvalación.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pirules.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Silao.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX007</t>
+  </si>
+  <si>
+    <t>CMX-Acoxpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arboledas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Catarina.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Culhuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Florida.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gardenia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Michoacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Noria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Padierna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pedregal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pegaso.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanAndres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanPedro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaAna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantoDomingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tulyehualco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xotepingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Peñon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJeronimo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Becal.pdv</t>
+  </si>
+  <si>
+    <t>XLA-Xala.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX008</t>
+  </si>
+  <si>
+    <t>CMX-Centro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chile.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Union.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Uruguay.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vallejo.pdv</t>
+  </si>
+  <si>
+    <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
+  </si>
+  <si>
+    <t>ARR-Arriaga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Alva.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Argentina.pdvc</t>
+  </si>
+  <si>
+    <t>CMX-Cuba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Febrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Popotla.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX009</t>
+  </si>
+  <si>
+    <t>CMX-Aztahuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Balbuena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Playa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlacotal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Villa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zaragoza.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapicería.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX010</t>
+  </si>
+  <si>
+    <t>CMX-Anahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chapu.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Constituyentes.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Molino.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Polanco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Reforma.pdv</t>
+  </si>
+  <si>
     <t>CMX-TorreBlanca.pdv</t>
   </si>
   <si>
-    <t>CMX-Anahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Reforma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chapu.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Polanco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Constituyentes.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Molino.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Jalalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixcoac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Guajiras.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LasAguilas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Olivar.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Encinos.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Barranca.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cuajimalpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Loma.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaPaz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Cedros.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Hocaba.pdv</t>
+    <t>CMX-Colipo.pdv</t>
   </si>
   <si>
     <t>CMX-Chopo.pdv</t>
   </si>
   <si>
-    <t>CMX-Aragon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Colipo.pdv</t>
-  </si>
-  <si>
     <t>CMX-Atitlan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Aztecas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Galeana.pdV</t>
-  </si>
-  <si>
-    <t>CMX-Aldama.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX005</t>
-  </si>
-  <si>
-    <t>CMX-Napoles.pdv</t>
-  </si>
-  <si>
-    <t>CMX-DelValle.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pestalozzi.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaCruz.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alamos.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Division.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Portales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaRosa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LasArmas.pd</t>
-  </si>
-  <si>
-    <t>CDMEX006</t>
-  </si>
-  <si>
-    <t>CMX-Vulcanizacion.pdv</t>
-  </si>
-  <si>
-    <t>CMX-RomeroRubio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Playa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zaragoza.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Balbuena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepito.pdv</t>
-  </si>
-  <si>
-    <t>CMX-AgricolaOriental.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zapata.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlacotal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Magdalena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Polvorilla.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaIsabel.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Palmitas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Leyes.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepalcates.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Aztahuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Ayala.pdv</t>
-  </si>
-  <si>
-    <t>CMX-LaTraviata.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Torres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vergel.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLorenzo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Villa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Santiago.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Lieja.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pirules.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gama.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sasatras.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tapiceria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Independencia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Silao.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Circunvalacion.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Atlixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arrieta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Dinares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Caporales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Topacio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLuis.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tejada.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX007</t>
-  </si>
-  <si>
-    <t>CMX-Catarina.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Florida.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pegaso.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xotepingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaAna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantoDomingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pedregal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Culhuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Padierna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Peñon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Michoacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Acoxpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arboledas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gardenia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJeronimo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanPedro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanAndres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Noria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tulyehualco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MilpaAlta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdy</t>
-  </si>
-  <si>
-    <t>CMX-Novelo.pdy</t>
-  </si>
-  <si>
-    <t>CMX-Avila.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepexpan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Juarez.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Juarez.pdy</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX008</t>
-  </si>
-  <si>
-    <t>CMX-Centro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chile.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Union.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Uruguay.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vallejo.pdv</t>
-  </si>
-  <si>
-    <t>IXS-IxtapanSal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vizcainas.pdv</t>
-  </si>
-  <si>
-    <t>ARR-Arriaga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alva.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Argentina.pdvc</t>
-  </si>
-  <si>
-    <t>CMX-Cuba.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Febrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Popotla.pdv</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="8.42592592592593" customWidth="1"/>
@@ -1921,10 +1939,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1932,10 +1950,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1943,10 +1961,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1954,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1965,7 +1983,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>27</v>
@@ -1976,7 +1994,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>28</v>
@@ -1987,7 +2005,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>29</v>
@@ -1998,7 +2016,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>30</v>
@@ -2009,7 +2027,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>31</v>
@@ -2020,7 +2038,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>32</v>
@@ -2306,10 +2324,10 @@
         <v>41</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2317,10 +2335,10 @@
         <v>41</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -2328,10 +2346,10 @@
         <v>41</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2339,10 +2357,10 @@
         <v>41</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2350,10 +2368,10 @@
         <v>41</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2361,10 +2379,10 @@
         <v>41</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2372,10 +2390,10 @@
         <v>41</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2383,10 +2401,10 @@
         <v>41</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2394,7 +2412,7 @@
         <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>70</v>
@@ -2405,7 +2423,7 @@
         <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>71</v>
@@ -2416,7 +2434,7 @@
         <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>72</v>
@@ -2427,10 +2445,10 @@
         <v>41</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2438,10 +2456,10 @@
         <v>41</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2449,10 +2467,10 @@
         <v>41</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -2460,10 +2478,10 @@
         <v>41</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2471,10 +2489,10 @@
         <v>41</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2482,10 +2500,10 @@
         <v>41</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -2493,7 +2511,7 @@
         <v>41</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>80</v>
@@ -2504,7 +2522,7 @@
         <v>41</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>81</v>
@@ -2515,7 +2533,7 @@
         <v>41</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>82</v>
@@ -2526,7 +2544,7 @@
         <v>41</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>83</v>
@@ -2537,7 +2555,7 @@
         <v>41</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>84</v>
@@ -2548,7 +2566,7 @@
         <v>41</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>85</v>
@@ -2559,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>86</v>
@@ -2570,7 +2588,7 @@
         <v>41</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>87</v>
@@ -2581,7 +2599,7 @@
         <v>41</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>88</v>
@@ -2592,7 +2610,7 @@
         <v>41</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>89</v>
@@ -2603,7 +2621,7 @@
         <v>41</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>90</v>
@@ -2614,7 +2632,7 @@
         <v>41</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>91</v>
@@ -2625,7 +2643,7 @@
         <v>41</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>92</v>
@@ -2636,7 +2654,7 @@
         <v>41</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>93</v>
@@ -2647,7 +2665,7 @@
         <v>41</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>94</v>
@@ -2658,7 +2676,7 @@
         <v>41</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>95</v>
@@ -2669,7 +2687,7 @@
         <v>41</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>96</v>
@@ -2680,7 +2698,7 @@
         <v>41</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>97</v>
@@ -2691,7 +2709,7 @@
         <v>41</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>98</v>
@@ -2702,10 +2720,10 @@
         <v>41</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2713,10 +2731,10 @@
         <v>41</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2724,10 +2742,10 @@
         <v>41</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2735,10 +2753,10 @@
         <v>41</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2746,10 +2764,10 @@
         <v>41</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2757,10 +2775,10 @@
         <v>41</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2768,10 +2786,10 @@
         <v>41</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2779,10 +2797,10 @@
         <v>41</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2790,10 +2808,10 @@
         <v>41</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2801,10 +2819,10 @@
         <v>41</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2812,10 +2830,10 @@
         <v>41</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2823,10 +2841,10 @@
         <v>41</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2834,10 +2852,10 @@
         <v>41</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -2845,10 +2863,10 @@
         <v>41</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2856,10 +2874,10 @@
         <v>41</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2867,10 +2885,10 @@
         <v>41</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2878,10 +2896,10 @@
         <v>41</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -2889,10 +2907,10 @@
         <v>41</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -2900,10 +2918,10 @@
         <v>41</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -2911,18 +2929,18 @@
         <v>41</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>120</v>
@@ -2930,10 +2948,10 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>121</v>
@@ -2941,10 +2959,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>122</v>
@@ -2952,10 +2970,10 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>123</v>
@@ -2963,10 +2981,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>124</v>
@@ -2974,10 +2992,10 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C115" t="s">
         <v>125</v>
@@ -2985,10 +3003,10 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C116" t="s">
         <v>126</v>
@@ -2996,10 +3014,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C117" t="s">
         <v>127</v>
@@ -3007,10 +3025,10 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C118" t="s">
         <v>128</v>
@@ -3018,10 +3036,10 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C119" t="s">
         <v>129</v>
@@ -3029,10 +3047,10 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C120" t="s">
         <v>130</v>
@@ -3040,79 +3058,79 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C121" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C122" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C123" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C124" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B125" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B126" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B127" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3120,10 +3138,10 @@
         <v>3</v>
       </c>
       <c r="B128" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C128" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3131,10 +3149,10 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3142,10 +3160,10 @@
         <v>3</v>
       </c>
       <c r="B130" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C130" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3153,10 +3171,10 @@
         <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3164,10 +3182,10 @@
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3175,76 +3193,76 @@
         <v>3</v>
       </c>
       <c r="B133" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C134" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B135" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C135" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C136" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C137" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C138" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3252,10 +3270,10 @@
         <v>41</v>
       </c>
       <c r="B140" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C140" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3263,10 +3281,10 @@
         <v>41</v>
       </c>
       <c r="B141" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3274,10 +3292,10 @@
         <v>41</v>
       </c>
       <c r="B142" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3285,10 +3303,10 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C143" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3296,10 +3314,10 @@
         <v>41</v>
       </c>
       <c r="B144" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C144" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3307,10 +3325,10 @@
         <v>41</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3318,76 +3336,120 @@
         <v>41</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C146" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C147" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C148" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C149" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C150" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C151" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" t="s">
+        <v>41</v>
+      </c>
+      <c r="B153" t="s">
+        <v>159</v>
+      </c>
+      <c r="C153" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" t="s">
+        <v>41</v>
+      </c>
+      <c r="B154" t="s">
+        <v>159</v>
+      </c>
+      <c r="C154" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" t="s">
+        <v>41</v>
+      </c>
+      <c r="B155" t="s">
+        <v>159</v>
+      </c>
+      <c r="C155" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>41</v>
+      </c>
+      <c r="B156" t="s">
+        <v>159</v>
+      </c>
+      <c r="C156" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$151</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="169">
   <si>
     <t>SPV</t>
   </si>
@@ -393,9 +393,6 @@
   </si>
   <si>
     <t>CMX-Becal.pdv</t>
-  </si>
-  <si>
-    <t>XLA-Xala.pdv</t>
   </si>
   <si>
     <t>CMX-Independencia.pdv</t>
@@ -547,10 +544,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-\$* #,##0.00_-;\-\$* #,##0.00_-;_-\$* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-\$* #,##0_-;\-\$* #,##0_-;_-\$* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1038,19 +1035,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1728,7 +1725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="8.42592592592593" customWidth="1"/>
@@ -2980,13 +2977,13 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B114" s="2" t="s">
+      <c r="A114" t="s">
+        <v>41</v>
+      </c>
+      <c r="B114" t="s">
         <v>99</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3050,10 +3047,10 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C120" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3061,7 +3058,7 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s">
         <v>132</v>
@@ -3072,7 +3069,7 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s">
         <v>133</v>
@@ -3083,7 +3080,7 @@
         <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C123" t="s">
         <v>134</v>
@@ -3094,7 +3091,7 @@
         <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C124" t="s">
         <v>135</v>
@@ -3105,7 +3102,7 @@
         <v>41</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
         <v>136</v>
@@ -3116,7 +3113,7 @@
         <v>41</v>
       </c>
       <c r="B126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
         <v>137</v>
@@ -3124,10 +3121,10 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C127" t="s">
         <v>138</v>
@@ -3138,7 +3135,7 @@
         <v>3</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C128" t="s">
         <v>139</v>
@@ -3149,7 +3146,7 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C129" t="s">
         <v>140</v>
@@ -3160,7 +3157,7 @@
         <v>3</v>
       </c>
       <c r="B130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C130" t="s">
         <v>141</v>
@@ -3171,7 +3168,7 @@
         <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C131" t="s">
         <v>142</v>
@@ -3182,7 +3179,7 @@
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C132" t="s">
         <v>143</v>
@@ -3190,13 +3187,13 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3204,7 +3201,7 @@
         <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C134" t="s">
         <v>146</v>
@@ -3215,7 +3212,7 @@
         <v>41</v>
       </c>
       <c r="B135" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C135" t="s">
         <v>147</v>
@@ -3226,7 +3223,7 @@
         <v>41</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C136" t="s">
         <v>148</v>
@@ -3237,7 +3234,7 @@
         <v>41</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C137" t="s">
         <v>149</v>
@@ -3248,7 +3245,7 @@
         <v>41</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C138" t="s">
         <v>150</v>
@@ -3259,7 +3256,7 @@
         <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C139" t="s">
         <v>151</v>
@@ -3270,7 +3267,7 @@
         <v>41</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C140" t="s">
         <v>152</v>
@@ -3281,7 +3278,7 @@
         <v>41</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C141" t="s">
         <v>153</v>
@@ -3292,7 +3289,7 @@
         <v>41</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C142" t="s">
         <v>154</v>
@@ -3303,7 +3300,7 @@
         <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C143" t="s">
         <v>155</v>
@@ -3314,7 +3311,7 @@
         <v>41</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s">
         <v>156</v>
@@ -3325,7 +3322,7 @@
         <v>41</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" t="s">
         <v>157</v>
@@ -3336,10 +3333,10 @@
         <v>41</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C146" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3347,7 +3344,7 @@
         <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C147" t="s">
         <v>160</v>
@@ -3358,7 +3355,7 @@
         <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C148" t="s">
         <v>161</v>
@@ -3369,7 +3366,7 @@
         <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C149" t="s">
         <v>162</v>
@@ -3380,7 +3377,7 @@
         <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C150" t="s">
         <v>163</v>
@@ -3391,7 +3388,7 @@
         <v>41</v>
       </c>
       <c r="B151" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C151" t="s">
         <v>164</v>
@@ -3402,7 +3399,7 @@
         <v>41</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
         <v>165</v>
@@ -3413,7 +3410,7 @@
         <v>41</v>
       </c>
       <c r="B153" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C153" t="s">
         <v>166</v>
@@ -3424,7 +3421,7 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C154" t="s">
         <v>167</v>
@@ -3435,21 +3432,10 @@
         <v>41</v>
       </c>
       <c r="B155" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C155" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
-      <c r="A156" t="s">
-        <v>41</v>
-      </c>
-      <c r="B156" t="s">
-        <v>159</v>
-      </c>
-      <c r="C156" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -2714,7 +2714,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>99</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>99</v>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>99</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>99</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>99</v>
@@ -2769,7 +2769,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>99</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>99</v>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>99</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>99</v>
@@ -2813,7 +2813,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>99</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>99</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>99</v>
@@ -2846,7 +2846,7 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>99</v>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>99</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>99</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>99</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>99</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>99</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>99</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>99</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>99</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>99</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>99</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>99</v>
@@ -2977,8 +2977,8 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" t="s">
-        <v>41</v>
+      <c r="A114" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B114" t="s">
         <v>99</v>
@@ -2988,8 +2988,8 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" t="s">
-        <v>41</v>
+      <c r="A115" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B115" t="s">
         <v>99</v>
@@ -2999,8 +2999,8 @@
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" t="s">
-        <v>41</v>
+      <c r="A116" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B116" t="s">
         <v>99</v>
@@ -3010,8 +3010,8 @@
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" t="s">
-        <v>41</v>
+      <c r="A117" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B117" t="s">
         <v>99</v>
@@ -3021,8 +3021,8 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" t="s">
-        <v>41</v>
+      <c r="A118" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B118" t="s">
         <v>99</v>
@@ -3032,8 +3032,8 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" t="s">
-        <v>41</v>
+      <c r="A119" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B119" t="s">
         <v>99</v>

--- a/SUPERVISORES.xlsx
+++ b/SUPERVISORES.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="170">
   <si>
     <t>SPV</t>
   </si>
@@ -317,193 +317,196 @@
     <t>CMX-Pirules.pdv</t>
   </si>
   <si>
+    <t>CMX-Caporales.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Topacio.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gama.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX007</t>
+  </si>
+  <si>
+    <t>CMX-Acoxpa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arboledas.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Catarina.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Culhuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Florida.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Gardenia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Michoacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-MilpaAlta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Noria.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Padierna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pedregal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Pegaso.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanAndres.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanPedro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantaAna.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SantoDomingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tulyehualco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Xotepingo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Peñon.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanJeronimo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Becal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Independencia.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Avila.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Fenix.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlahuac.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Novelo.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tepexpan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Mixco.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Juarez.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX008</t>
+  </si>
+  <si>
+    <t>CMX-Centro.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Chile.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Union.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Uruguay.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vallejo.pdv</t>
+  </si>
+  <si>
+    <t>IXS-IxtapanSal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Vizcainas.pdv</t>
+  </si>
+  <si>
+    <t>ARR-Arriaga.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Alva.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Argentina.pdvc</t>
+  </si>
+  <si>
+    <t>CMX-Cuba.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Febrero.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Popotla.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Nacionales.pdv</t>
+  </si>
+  <si>
+    <t>CDMEX009</t>
+  </si>
+  <si>
+    <t>CMX-Aztahuacan.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Balbuena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Playa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tlacotal.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Villa.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Zaragoza.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Dinares.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tapicería.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Tejada.pdv</t>
+  </si>
+  <si>
+    <t>CMX-SanLuis.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Arrieta.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sena.pdv</t>
+  </si>
+  <si>
+    <t>CMX-Sasatras.pdv</t>
+  </si>
+  <si>
     <t>CMX-Silao.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Caporales.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Topacio.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gama.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX007</t>
-  </si>
-  <si>
-    <t>CMX-Acoxpa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arboledas.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Catarina.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Culhuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Florida.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Gardenia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Michoacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-MilpaAlta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Noria.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Padierna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pedregal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Pegaso.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanAndres.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanPedro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantaAna.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SantoDomingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tulyehualco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Xotepingo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Peñon.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanJeronimo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Becal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Independencia.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Avila.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Fenix.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlahuac.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Novelo.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tepexpan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Mixco.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Juarez.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX008</t>
-  </si>
-  <si>
-    <t>CMX-Centro.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Chile.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Union.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Uruguay.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vallejo.pdv</t>
-  </si>
-  <si>
-    <t>IXS-IxtapanSal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Vizcainas.pdv</t>
-  </si>
-  <si>
-    <t>ARR-Arriaga.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Alva.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Argentina.pdvc</t>
-  </si>
-  <si>
-    <t>CMX-Cuba.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Febrero.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Popotla.pdv</t>
-  </si>
-  <si>
-    <t>CDMEX009</t>
-  </si>
-  <si>
-    <t>CMX-Aztahuacan.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Balbuena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Playa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tlacotal.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Villa.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Zaragoza.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Dinares.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tapicería.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Tejada.pdv</t>
-  </si>
-  <si>
-    <t>CMX-SanLuis.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Arrieta.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sena.pdv</t>
-  </si>
-  <si>
-    <t>CMX-Sasatras.pdv</t>
   </si>
   <si>
     <t>CDMEX010</t>
@@ -1725,7 +1728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="8.42592592592593" customWidth="1"/>
@@ -2703,13 +2706,13 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2717,7 +2720,7 @@
         <v>3</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>100</v>
@@ -2728,7 +2731,7 @@
         <v>3</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>101</v>
@@ -2739,7 +2742,7 @@
         <v>3</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>102</v>
@@ -2750,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>103</v>
@@ -2761,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>104</v>
@@ -2772,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>105</v>
@@ -2783,7 +2786,7 @@
         <v>3</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>106</v>
@@ -2794,7 +2797,7 @@
         <v>3</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>107</v>
@@ -2805,7 +2808,7 @@
         <v>3</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>108</v>
@@ -2816,7 +2819,7 @@
         <v>3</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>109</v>
@@ -2827,7 +2830,7 @@
         <v>3</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>110</v>
@@ -2838,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>111</v>
@@ -2849,7 +2852,7 @@
         <v>3</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>112</v>
@@ -2860,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>113</v>
@@ -2871,7 +2874,7 @@
         <v>3</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>114</v>
@@ -2882,7 +2885,7 @@
         <v>3</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>115</v>
@@ -2893,7 +2896,7 @@
         <v>3</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>116</v>
@@ -2904,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>117</v>
@@ -2915,7 +2918,7 @@
         <v>3</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>118</v>
@@ -2926,7 +2929,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>119</v>
@@ -2937,7 +2940,7 @@
         <v>3</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>120</v>
@@ -2948,7 +2951,7 @@
         <v>3</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>121</v>
@@ -2959,7 +2962,7 @@
         <v>3</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>122</v>
@@ -2970,7 +2973,7 @@
         <v>3</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>123</v>
@@ -2981,7 +2984,7 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C114" t="s">
         <v>124</v>
@@ -2992,7 +2995,7 @@
         <v>3</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C115" t="s">
         <v>125</v>
@@ -3003,7 +3006,7 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
         <v>126</v>
@@ -3014,7 +3017,7 @@
         <v>3</v>
       </c>
       <c r="B117" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
         <v>127</v>
@@ -3025,7 +3028,7 @@
         <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
         <v>128</v>
@@ -3033,13 +3036,13 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="2" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C119" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3047,7 +3050,7 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C120" t="s">
         <v>131</v>
@@ -3058,7 +3061,7 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
         <v>132</v>
@@ -3069,7 +3072,7 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
         <v>133</v>
@@ -3080,7 +3083,7 @@
         <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
         <v>134</v>
@@ -3091,7 +3094,7 @@
         <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C124" t="s">
         <v>135</v>
@@ -3102,7 +3105,7 @@
         <v>41</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
         <v>136</v>
@@ -3110,10 +3113,10 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C126" t="s">
         <v>137</v>
@@ -3124,7 +3127,7 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C127" t="s">
         <v>138</v>
@@ -3135,7 +3138,7 @@
         <v>3</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
         <v>139</v>
@@ -3146,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C129" t="s">
         <v>140</v>
@@ -3157,7 +3160,7 @@
         <v>3</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C130" t="s">
         <v>141</v>
@@ -3168,7 +3171,7 @@
         <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C131" t="s">
         <v>142</v>
@@ -3179,7 +3182,7 @@
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C132" t="s">
         <v>143</v>
@@ -3333,10 +3336,10 @@
         <v>41</v>
       </c>
       <c r="B146" t="s">
+        <v>144</v>
+      </c>
+      <c r="C146" t="s">
         <v>158</v>
-      </c>
-      <c r="C146" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3344,7 +3347,7 @@
         <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C147" t="s">
         <v>160</v>
@@ -3355,7 +3358,7 @@
         <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C148" t="s">
         <v>161</v>
@@ -3366,7 +3369,7 @@
         <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C149" t="s">
         <v>162</v>
@@ -3377,7 +3380,7 @@
         <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C150" t="s">
         <v>163</v>
@@ -3388,7 +3391,7 @@
         <v>41</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C151" t="s">
         <v>164</v>
@@ -3399,7 +3402,7 @@
         <v>41</v>
       </c>
       <c r="B152" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C152" t="s">
         <v>165</v>
@@ -3410,7 +3413,7 @@
         <v>41</v>
       </c>
       <c r="B153" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C153" t="s">
         <v>166</v>
@@ -3421,7 +3424,7 @@
         <v>41</v>
       </c>
       <c r="B154" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C154" t="s">
         <v>167</v>
@@ -3432,10 +3435,21 @@
         <v>41</v>
       </c>
       <c r="B155" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C155" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" t="s">
+        <v>41</v>
+      </c>
+      <c r="B156" t="s">
+        <v>159</v>
+      </c>
+      <c r="C156" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
